--- a/data/xlsx/transport-stats-data.xlsx
+++ b/data/xlsx/transport-stats-data.xlsx
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -819,7 +819,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -827,7 +827,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -835,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -843,7 +843,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -859,7 +859,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -867,7 +867,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -875,7 +875,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -883,7 +883,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -891,7 +891,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -899,7 +899,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -915,7 +915,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -923,7 +923,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -931,7 +931,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -939,7 +939,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -955,7 +955,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -963,7 +963,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
@@ -979,7 +979,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -987,7 +987,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
@@ -995,7 +995,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1011,7 +1011,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1019,7 +1019,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -1027,7 +1027,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1035,7 +1035,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -1043,7 +1043,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1051,7 +1051,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -1059,7 +1059,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1067,7 +1067,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
@@ -1075,7 +1075,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -1083,7 +1083,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -1091,7 +1091,7 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1099,7 +1099,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1107,7 +1107,7 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -1115,7 +1115,7 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
@@ -1131,7 +1131,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -1139,7 +1139,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -1147,7 +1147,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -1155,7 +1155,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
@@ -1163,7 +1163,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="4" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -1171,7 +1171,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
@@ -1179,7 +1179,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="4" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
@@ -1187,7 +1187,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
@@ -1195,7 +1195,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -1203,7 +1203,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -1211,7 +1211,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="4" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -1219,7 +1219,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="4" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -1227,7 +1227,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -1235,7 +1235,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="4" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/xlsx/transport-stats-data.xlsx
+++ b/data/xlsx/transport-stats-data.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -490,97 +490,97 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>One sheet per dataset. The sheet name tells you which tutorial uses it.</t>
+          <t>If there is a yellow 'PROTECTED VIEW' bar at the top of this window, click</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Enable Editing - Excel opens downloaded files read-only until you do.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sheet                     Used by</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T1 Travel Times           Tutorial 1, Questions 2 and 6</t>
+          <t>One sheet per dataset. The sheet name tells you which tutorial uses it.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T1 Histogram Guide        Tutorial 1, Questions 3, 4 and 5</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T3 Fuel Consumption       Tutorial 3, Question 3</t>
+          <t>Sheet                     Used by</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T3 HGV Weights            Tutorial 3, Questions 4 and 5</t>
+          <t>T1 Travel Times           Tutorial 1, Questions 2 and 6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T4 Junction Waiting       Tutorial 4, Question 5</t>
+          <t>T1 Histogram Guide        Tutorial 1, Questions 3, 4 and 5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T5 Taxi Queue             Tutorial 5, Question 1</t>
+          <t>T3 Fuel Consumption       Tutorial 3, Question 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T5 Car Ownership          Tutorial 5, Question 2</t>
+          <t>T3 HGV Weights            Tutorial 3, Questions 4 and 5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T5 Accidents Weather      Tutorial 5, Question 3</t>
+          <t>T4 Junction Waiting       Tutorial 4, Question 5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T5 Reaction Distance      Tutorial 5, Question 4</t>
+          <t>T5 Taxi Queue             Tutorial 5, Question 1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T5 Car Ownership          Tutorial 5, Question 2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>On the travel time sheet the observations sit in B4:B58, so the cell</t>
+          <t>T5 Accidents Weather      Tutorial 5, Question 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>references used in the tutorial worked solutions apply exactly as written.</t>
+          <t>T5 Reaction Distance      Tutorial 5, Question 4</t>
         </is>
       </c>
     </row>
@@ -589,6 +589,23 @@
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>On the travel time sheet the observations sit in B4:B58, so the cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>references used in the tutorial worked solutions apply exactly as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>The same data is available as CSV in data/csv/ if you prefer R or Python.</t>
         </is>

--- a/data/xlsx/transport-stats-data.xlsx
+++ b/data/xlsx/transport-stats-data.xlsx
@@ -590,14 +590,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>On the travel time sheet the observations sit in B4:B58, so the cell</t>
+          <t>On the travel time sheet, the values are in B4:B58. The solutions in the</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>references used in the tutorial worked solutions apply exactly as written.</t>
+          <t>tutorials use this range.</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The same data is available as CSV in data/csv/ if you prefer R or Python.</t>
+          <t>The same data is in data/csv/ as CSV files, for R and Python.</t>
         </is>
       </c>
     </row>
